--- a/CONCENTRADO_EMPLEADOS.xlsx
+++ b/CONCENTRADO_EMPLEADOS.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4604c7d1701c1fd5/Desktop/bagira_agent/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4604c7d1701c1fd5/Desktop/BagheeraAgent/BageheeraAgent/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="19" documentId="11_11F15350D473D61EE10F68D7565DCE3A874760D9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{56F50349-EA9C-4EFA-B825-3831A7C16439}"/>
+  <xr:revisionPtr revIDLastSave="33" documentId="11_11F15350D473D61EE10F68D7565DCE3A874760D9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D140A83F-CCB6-4131-AAE6-9DB3A81CE4D6}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="173">
   <si>
     <t>ID</t>
   </si>
@@ -527,6 +527,18 @@
   </si>
   <si>
     <t xml:space="preserve"> ROCHA BONILLA ARIANA ISABEL</t>
+  </si>
+  <si>
+    <t>MARTINEZ HERNANDEZ DANNA PAOLA</t>
+  </si>
+  <si>
+    <t>RUNNER</t>
+  </si>
+  <si>
+    <t>MAHD051009MTSRRNA8</t>
+  </si>
+  <si>
+    <t>C AQUILES SERDAN #202 COL AMPLIACION LAGUNA DE LA PUERTA</t>
   </si>
 </sst>
 </file>
@@ -534,7 +546,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -567,8 +579,8 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -871,11 +883,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K46"/>
+  <dimension ref="A1:K47"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="36.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.109375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="18" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="22.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="70.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
@@ -1342,7 +1357,7 @@
       <c r="A15">
         <v>19.100000000000001</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" t="s">
         <v>54</v>
       </c>
       <c r="C15" t="s">
@@ -2414,6 +2429,41 @@
       </c>
       <c r="K46" t="s">
         <v>156</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A47">
+        <v>63</v>
+      </c>
+      <c r="B47" t="s">
+        <v>169</v>
+      </c>
+      <c r="C47" t="s">
+        <v>44</v>
+      </c>
+      <c r="D47" t="s">
+        <v>170</v>
+      </c>
+      <c r="E47" s="2">
+        <v>46095</v>
+      </c>
+      <c r="F47" t="s">
+        <v>20</v>
+      </c>
+      <c r="G47" s="2">
+        <v>46187</v>
+      </c>
+      <c r="H47" t="s">
+        <v>14</v>
+      </c>
+      <c r="I47" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J47" t="s">
+        <v>171</v>
+      </c>
+      <c r="K47" s="2" t="s">
+        <v>172</v>
       </c>
     </row>
   </sheetData>

--- a/CONCENTRADO_EMPLEADOS.xlsx
+++ b/CONCENTRADO_EMPLEADOS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4604c7d1701c1fd5/Desktop/BagheeraAgent/BageheeraAgent/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="33" documentId="11_11F15350D473D61EE10F68D7565DCE3A874760D9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D140A83F-CCB6-4131-AAE6-9DB3A81CE4D6}"/>
+  <xr:revisionPtr revIDLastSave="74" documentId="11_11F15350D473D61EE10F68D7565DCE3A874760D9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ADA6BC53-8322-403D-9885-6F1BD0D21CD7}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="176">
   <si>
     <t>ID</t>
   </si>
@@ -184,27 +184,18 @@
     <t>C. ORQUIDEAS #316 COL LAS FLORES 89510 CD MADERO</t>
   </si>
   <si>
-    <t>CONSUELO INFANTE REBUllOSA</t>
-  </si>
-  <si>
     <t>IARC800715MTSNBN06</t>
   </si>
   <si>
     <t>C 8A #102 COL SAHOP 89506 CD MADERO</t>
   </si>
   <si>
-    <t xml:space="preserve">MARIA MAGDALENA QUIROZ BANDA </t>
-  </si>
-  <si>
     <t>QUBM 730417MTSRNG15</t>
   </si>
   <si>
     <t>C GARDENEAS #104 OTE COL LAS FLORES 89510 CD MADERO</t>
   </si>
   <si>
-    <t>JESSICA GUERRERO HERNANDEZ</t>
-  </si>
-  <si>
     <t>GERENTE GENERAL</t>
   </si>
   <si>
@@ -214,63 +205,42 @@
     <t>C. COLOMBIA #836 COL SOLIDARIDAD VOLUNTAD Y TRABAJO 89317 TAMPICO</t>
   </si>
   <si>
-    <t>ANGEL DAVID MARTINEZ GUERRERO</t>
-  </si>
-  <si>
     <t>MESERO</t>
   </si>
   <si>
     <t>…...</t>
   </si>
   <si>
-    <t>ANA ELIZABETH OCAÑA JIMENEZ</t>
-  </si>
-  <si>
     <t>OAJA050803MTSCMNA9</t>
   </si>
   <si>
     <t>C. GUERRERO #306 NTE. COL. UNIDAD NACIONAL 89410 CD MADERO</t>
   </si>
   <si>
-    <t>BLANCA ESTHELA PUENTE MARTINEZ</t>
-  </si>
-  <si>
     <t>PUMB770511MGTNRL07</t>
   </si>
   <si>
     <t>C. AMERICO VILLAREAL #200 COL LIENZO CHARRO 89506 CD MADERO</t>
   </si>
   <si>
-    <t>KARLA VICTORIA DE LA CRUZ TORRES</t>
-  </si>
-  <si>
     <t>CUTK050910MTSRRRA7</t>
   </si>
   <si>
     <t>C. NARDOS #813 NTE COL LAS FLORES 89510 CD MADERO</t>
   </si>
   <si>
-    <t>MARIA SOLEDAD RAMOS MIRANDA</t>
-  </si>
-  <si>
     <t>RAMS660524MVZMRL05</t>
   </si>
   <si>
     <t>C. FERRER GUARDIA #1404 PTE. COL. PRIMERO DE MAYO CD MADERO</t>
   </si>
   <si>
-    <t>MARIA GUADALUPE RODROGUEZ TAPIA</t>
-  </si>
-  <si>
     <t>ROTG030306MTSDPDA7</t>
   </si>
   <si>
     <t>PRIV. LUIS DONALDO COLOSIO #1117 AMP. CANDELARIO GARZA 89505 CD MADERO</t>
   </si>
   <si>
-    <t>DAVID TORRES ROMERO</t>
-  </si>
-  <si>
     <t>REPARTO</t>
   </si>
   <si>
@@ -283,27 +253,18 @@
     <t>C ADUANA #315 COL FERROCARILERA 89590 CD MADERO</t>
   </si>
   <si>
-    <t>VICTOR DELGADO LEDEZMA</t>
-  </si>
-  <si>
     <t>DELV730614HTSLDC00</t>
   </si>
   <si>
     <t>PRIV LINARES 9 COL CAMPBELL 89260 TAMPICO</t>
   </si>
   <si>
-    <t>VIRGINIA ONTIVEROS HERNANDEZ</t>
-  </si>
-  <si>
     <t>OIHV661005MTSNRR02</t>
   </si>
   <si>
     <t>C. ISAAC SANCHEZ GARZA #125 COL NATIVIDAD GARZA LEAL 89317 TAMPICO</t>
   </si>
   <si>
-    <t>EMMA PATRICIA ESPINOZA LUCIO</t>
-  </si>
-  <si>
     <t>PUNTO DE VENTA</t>
   </si>
   <si>
@@ -316,99 +277,66 @@
     <t>C. LUCIO BLANCO #315 COL. JOSE LOPEZ PORTILLO 89338 TAMPICO</t>
   </si>
   <si>
-    <t>LIZ ZURELLA RODRIGUEZ QUINTANAR</t>
-  </si>
-  <si>
     <t>ROQL691130MTSDNZ05</t>
   </si>
   <si>
     <t>C. CANGREJO #313 B FRACC PLAYA MIRAMAR 89540 CD MADERO</t>
   </si>
   <si>
-    <t>LUCERO GARCIA ALVADADO</t>
-  </si>
-  <si>
     <t>GAAL990917MVZRLC06</t>
   </si>
   <si>
     <t>C. HONESTIDAD III COL INTEGRACCION FAMILIAR CD MADERO</t>
   </si>
   <si>
-    <t>MARIA ELODIA ALVARADO GARCIA</t>
-  </si>
-  <si>
     <t>AAGE800424MVZLRL06</t>
   </si>
   <si>
     <t>C. MOCTEZUMA #403 NTE COL 16 DE SEPTIEMBRE 89512 CD MADERO</t>
   </si>
   <si>
-    <t>MICAELA GARCIA PERALEZ</t>
-  </si>
-  <si>
     <t>GAPM690311MTSRRC05</t>
   </si>
   <si>
     <t>AV ADOLFO LOPEZ MATEOS #110 4 COL CANDELARIO GARZA 89505 CD MADERO</t>
   </si>
   <si>
-    <t>ANGELICA VIRIDIANA MARTINEZ NAVA</t>
-  </si>
-  <si>
     <t>MANA860827MTSRVN08</t>
   </si>
   <si>
     <t>MERIDA #611 COL MIGUEL HIDALGO CD MADERO</t>
   </si>
   <si>
-    <t>MARTA ESTELA ANDRADE ZAMORA</t>
-  </si>
-  <si>
     <t>AAZM650919MTSNMR08</t>
   </si>
   <si>
     <t>C. CANDELARIO GARZA #600 COL. HERIBERTO KEHOE 89510 CD MADERO</t>
   </si>
   <si>
-    <t>VERONICA GARCIA GARCIA</t>
-  </si>
-  <si>
     <t>GAGV760727MTSRRR04</t>
   </si>
   <si>
     <t>C TAJIN #214 COL 16 DE SEPTIEMBRE CD MADERO</t>
   </si>
   <si>
-    <t>YOLANDA PASCUAL GREGORIO</t>
-  </si>
-  <si>
     <t>PAGY670321MVZSRL08</t>
   </si>
   <si>
     <t>C 18 DE MARZO #1206 NTE COL VICENTE GUERRERO 89580 CD MADERO</t>
   </si>
   <si>
-    <t>EMILI GUADALUPE MALDONADO PUGA</t>
-  </si>
-  <si>
     <t>MAPE051127MTSLGMA2</t>
   </si>
   <si>
     <t xml:space="preserve">C 12 SEC BENITO BLANCO </t>
   </si>
   <si>
-    <t>ALONDRA NAOMI SANTIAGO PIÑON</t>
-  </si>
-  <si>
     <t>SAPA020606MTSNXLA2</t>
   </si>
   <si>
     <t>C LEDRO DE TEJADA #413 COL EMILIO PORTES GIL 89316</t>
   </si>
   <si>
-    <t>ASHLEE LIDIBETH DIAZ MONTES</t>
-  </si>
-  <si>
     <t>DIMA070702MTSZNSA3</t>
   </si>
   <si>
@@ -442,36 +370,24 @@
     <t>C EMILIANO ZAPATA #410 COL CANDELARIO GARZA CD MADERO</t>
   </si>
   <si>
-    <t>AMERICA VENECIA ALVARADO RODRIGUEZ</t>
-  </si>
-  <si>
     <t>AARA000918MTSLDMA8</t>
   </si>
   <si>
     <t>C 10 #643 COL HERIBERTO KEHOE CD MADERO</t>
   </si>
   <si>
-    <t>ALONDRA CAROMI PIGA ACUÑA</t>
-  </si>
-  <si>
     <t>PUAA080527MTSGCLA2</t>
   </si>
   <si>
     <t>COL EMILIANO ZAPATA  C ANASTACIO BUSTAMANTE #412</t>
   </si>
   <si>
-    <t>ALFONSO GUILLEN HERRERA</t>
-  </si>
-  <si>
     <t>GUHA701117HTSLRL09</t>
   </si>
   <si>
     <t>CALLE RIO VERDE #204 COL ANDELARIO GARZA 89500 CD MADERO</t>
   </si>
   <si>
-    <t>PEDRO SALAS CORONADO</t>
-  </si>
-  <si>
     <t>GENERAL</t>
   </si>
   <si>
@@ -484,9 +400,6 @@
     <t>ANDADOR FCO VILLA #123 COL JOSE LOPEZ PORTILLO TAMPICO</t>
   </si>
   <si>
-    <t>KARLA IRENE GARCIA MARTINEZ</t>
-  </si>
-  <si>
     <t>GAMK000808MTSRRRA4</t>
   </si>
   <si>
@@ -539,6 +452,102 @@
   </si>
   <si>
     <t>C AQUILES SERDAN #202 COL AMPLIACION LAGUNA DE LA PUERTA</t>
+  </si>
+  <si>
+    <t>INFANTE REBUllOSA CONSUELO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QUIROZ BANDA MARIA MAGDALENA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">GUERRERO HERNANDEZ JESSICA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARTINEZ GUERRERO ANGEL DAVID </t>
+  </si>
+  <si>
+    <t xml:space="preserve">OCAÑA JIMENEZ ANA ELIZABETH </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PUENTE MARTINEZ BLANCA ESTHELA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DE LA CRUZ TORRES KARLA VICTORIA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAMOS MIRANDA MARIA SOLEDAD </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RODROGUEZ TAPIA MARIA GUADALUPE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TORRES ROMERO DAVID </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DELGADO LEDEZMA VICTOR </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ONTIVEROS HERNANDEZ VIRGINIA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESPINOZA LUCIO EMMA PATRICIA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RODRIGUEZ QUINTANAR LIZ ZURELLA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">GARCIA ALVADADO LUCERO </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALVARADO GARCIA MARIA ELODIA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">GARCIA PERALEZ MICAELA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARTINEZ NAVA ANGELICA VIRIDIANA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANDRADE ZAMORA MARTA ESTELA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">GARCIA GARCIA VERONICA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PASCUAL GREGORIO YOLANDA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MALDONADO PUGA EMILI GUADALUPE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SANTIAGO PIÑON ALONDRA NAOMI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIAZ MONTES ASHLEE LIDIBETH </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALVARADO RODRIGUEZ AMERICA VENECIA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PUGA ACUÑA ALONDRA CAROMI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">GUILLEN HERRERA ALFONSO </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SALAS CORONADO PEDRO </t>
+  </si>
+  <si>
+    <t xml:space="preserve">GARCIA MARTINEZ KARLA IRENE </t>
+  </si>
+  <si>
+    <t>MARTINEZ CISNEROS MARIA LIZZETH</t>
+  </si>
+  <si>
+    <t>MACL090109MSPRSZA9</t>
+  </si>
+  <si>
+    <t>C. PEMEX #2609 A COL. BENITO JUAREZ</t>
   </si>
 </sst>
 </file>
@@ -596,6 +605,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -883,7 +896,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K47"/>
+  <dimension ref="A1:K48"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="36.5546875" bestFit="1" customWidth="1"/>
@@ -933,7 +946,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>157</v>
+        <v>128</v>
       </c>
       <c r="C2" t="s">
         <v>11</v>
@@ -1000,7 +1013,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>158</v>
+        <v>129</v>
       </c>
       <c r="C4" t="s">
         <v>23</v>
@@ -1032,7 +1045,7 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>159</v>
+        <v>130</v>
       </c>
       <c r="C5" t="s">
         <v>23</v>
@@ -1064,7 +1077,7 @@
         <v>6.5</v>
       </c>
       <c r="B6" t="s">
-        <v>160</v>
+        <v>131</v>
       </c>
       <c r="C6" t="s">
         <v>23</v>
@@ -1099,7 +1112,7 @@
         <v>7.9</v>
       </c>
       <c r="B7" t="s">
-        <v>161</v>
+        <v>132</v>
       </c>
       <c r="C7" t="s">
         <v>23</v>
@@ -1134,7 +1147,7 @@
         <v>9.3000000000000007</v>
       </c>
       <c r="B8" t="s">
-        <v>162</v>
+        <v>133</v>
       </c>
       <c r="C8" t="s">
         <v>23</v>
@@ -1166,7 +1179,7 @@
         <v>10.7</v>
       </c>
       <c r="B9" t="s">
-        <v>163</v>
+        <v>134</v>
       </c>
       <c r="C9" t="s">
         <v>23</v>
@@ -1198,7 +1211,7 @@
         <v>12.1</v>
       </c>
       <c r="B10" t="s">
-        <v>164</v>
+        <v>135</v>
       </c>
       <c r="C10" t="s">
         <v>23</v>
@@ -1230,7 +1243,7 @@
         <v>13.5</v>
       </c>
       <c r="B11" t="s">
-        <v>165</v>
+        <v>136</v>
       </c>
       <c r="C11" t="s">
         <v>11</v>
@@ -1262,7 +1275,7 @@
         <v>14.9</v>
       </c>
       <c r="B12" t="s">
-        <v>166</v>
+        <v>137</v>
       </c>
       <c r="C12" t="s">
         <v>44</v>
@@ -1294,7 +1307,7 @@
         <v>16.3</v>
       </c>
       <c r="B13" t="s">
-        <v>167</v>
+        <v>138</v>
       </c>
       <c r="C13" t="s">
         <v>44</v>
@@ -1326,7 +1339,7 @@
         <v>17.7</v>
       </c>
       <c r="B14" t="s">
-        <v>168</v>
+        <v>139</v>
       </c>
       <c r="C14" t="s">
         <v>23</v>
@@ -1358,7 +1371,7 @@
         <v>19.100000000000001</v>
       </c>
       <c r="B15" t="s">
-        <v>54</v>
+        <v>144</v>
       </c>
       <c r="C15" t="s">
         <v>23</v>
@@ -1379,10 +1392,10 @@
         <v>15</v>
       </c>
       <c r="J15" t="s">
+        <v>54</v>
+      </c>
+      <c r="K15" t="s">
         <v>55</v>
-      </c>
-      <c r="K15" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
@@ -1390,7 +1403,7 @@
         <v>20.5</v>
       </c>
       <c r="B16" t="s">
-        <v>57</v>
+        <v>145</v>
       </c>
       <c r="C16" t="s">
         <v>23</v>
@@ -1411,10 +1424,10 @@
         <v>15</v>
       </c>
       <c r="J16" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="K16" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
@@ -1422,13 +1435,13 @@
         <v>21.9</v>
       </c>
       <c r="B17" t="s">
-        <v>60</v>
+        <v>146</v>
       </c>
       <c r="C17" t="s">
         <v>11</v>
       </c>
       <c r="D17" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E17" s="1">
         <v>45129</v>
@@ -1443,10 +1456,10 @@
         <v>15</v>
       </c>
       <c r="J17" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="K17" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
@@ -1454,13 +1467,13 @@
         <v>23.3</v>
       </c>
       <c r="B18" t="s">
-        <v>64</v>
+        <v>147</v>
       </c>
       <c r="C18" t="s">
         <v>44</v>
       </c>
       <c r="D18" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="H18" t="s">
         <v>35</v>
@@ -1469,10 +1482,10 @@
         <v>36</v>
       </c>
       <c r="J18" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="K18" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
@@ -1480,13 +1493,13 @@
         <v>24.7</v>
       </c>
       <c r="B19" t="s">
-        <v>67</v>
+        <v>148</v>
       </c>
       <c r="C19" t="s">
         <v>44</v>
       </c>
       <c r="D19" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E19" s="1">
         <v>45969</v>
@@ -1504,10 +1517,10 @@
         <v>15</v>
       </c>
       <c r="J19" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="K19" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
@@ -1515,13 +1528,13 @@
         <v>26.1</v>
       </c>
       <c r="B20" t="s">
-        <v>70</v>
+        <v>149</v>
       </c>
       <c r="C20" t="s">
         <v>44</v>
       </c>
       <c r="D20" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E20" s="1">
         <v>45122</v>
@@ -1536,10 +1549,10 @@
         <v>15</v>
       </c>
       <c r="J20" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="K20" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
@@ -1547,13 +1560,13 @@
         <v>27.5</v>
       </c>
       <c r="B21" t="s">
-        <v>73</v>
+        <v>150</v>
       </c>
       <c r="C21" t="s">
         <v>44</v>
       </c>
       <c r="D21" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E21" s="1">
         <v>45978</v>
@@ -1571,10 +1584,10 @@
         <v>15</v>
       </c>
       <c r="J21" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="K21" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
@@ -1582,13 +1595,13 @@
         <v>28.9</v>
       </c>
       <c r="B22" t="s">
-        <v>76</v>
+        <v>151</v>
       </c>
       <c r="C22" t="s">
         <v>44</v>
       </c>
       <c r="D22" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E22" s="1">
         <v>45926</v>
@@ -1606,10 +1619,10 @@
         <v>15</v>
       </c>
       <c r="J22" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="K22" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
@@ -1617,13 +1630,13 @@
         <v>30.3</v>
       </c>
       <c r="B23" t="s">
-        <v>79</v>
+        <v>152</v>
       </c>
       <c r="C23" t="s">
         <v>44</v>
       </c>
       <c r="D23" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E23" s="1">
         <v>45984</v>
@@ -1641,10 +1654,10 @@
         <v>15</v>
       </c>
       <c r="J23" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="K23" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.3">
@@ -1652,13 +1665,13 @@
         <v>31.7</v>
       </c>
       <c r="B24" t="s">
-        <v>82</v>
+        <v>153</v>
       </c>
       <c r="C24" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D24" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="E24" s="1">
         <v>45856</v>
@@ -1673,10 +1686,10 @@
         <v>36</v>
       </c>
       <c r="J24" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K24" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.3">
@@ -1684,13 +1697,13 @@
         <v>33.1</v>
       </c>
       <c r="B25" t="s">
-        <v>87</v>
+        <v>154</v>
       </c>
       <c r="C25" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D25" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="E25" s="1">
         <v>45508</v>
@@ -1705,10 +1718,10 @@
         <v>36</v>
       </c>
       <c r="J25" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K25" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.3">
@@ -1716,7 +1729,7 @@
         <v>34.5</v>
       </c>
       <c r="B26" t="s">
-        <v>90</v>
+        <v>155</v>
       </c>
       <c r="C26" t="s">
         <v>11</v>
@@ -1737,10 +1750,10 @@
         <v>15</v>
       </c>
       <c r="J26" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K26" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.3">
@@ -1748,13 +1761,13 @@
         <v>35.9</v>
       </c>
       <c r="B27" t="s">
-        <v>93</v>
+        <v>156</v>
       </c>
       <c r="C27" t="s">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="D27" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="E27" s="1">
         <v>45758</v>
@@ -1772,10 +1785,10 @@
         <v>15</v>
       </c>
       <c r="J27" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="K27" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.3">
@@ -1783,13 +1796,13 @@
         <v>37.299999999999997</v>
       </c>
       <c r="B28" t="s">
-        <v>98</v>
+        <v>157</v>
       </c>
       <c r="C28" t="s">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="D28" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="E28" s="1">
         <v>45306</v>
@@ -1804,10 +1817,10 @@
         <v>15</v>
       </c>
       <c r="J28" t="s">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="K28" t="s">
-        <v>100</v>
+        <v>86</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.3">
@@ -1815,13 +1828,13 @@
         <v>38.700000000000003</v>
       </c>
       <c r="B29" t="s">
-        <v>101</v>
+        <v>158</v>
       </c>
       <c r="C29" t="s">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="D29" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="E29" s="1">
         <v>45736</v>
@@ -1839,10 +1852,10 @@
         <v>15</v>
       </c>
       <c r="J29" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="K29" t="s">
-        <v>103</v>
+        <v>88</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.3">
@@ -1850,13 +1863,13 @@
         <v>40.1</v>
       </c>
       <c r="B30" t="s">
-        <v>104</v>
+        <v>159</v>
       </c>
       <c r="C30" t="s">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="D30" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="E30" s="1">
         <v>46097</v>
@@ -1874,10 +1887,10 @@
         <v>15</v>
       </c>
       <c r="J30" t="s">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="K30" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.3">
@@ -1885,13 +1898,13 @@
         <v>41.5</v>
       </c>
       <c r="B31" t="s">
-        <v>107</v>
+        <v>160</v>
       </c>
       <c r="C31" t="s">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="D31" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="E31" s="1">
         <v>45876</v>
@@ -1906,10 +1919,10 @@
         <v>15</v>
       </c>
       <c r="J31" t="s">
-        <v>108</v>
+        <v>91</v>
       </c>
       <c r="K31" t="s">
-        <v>109</v>
+        <v>92</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.3">
@@ -1917,7 +1930,7 @@
         <v>42.9</v>
       </c>
       <c r="B32" t="s">
-        <v>110</v>
+        <v>161</v>
       </c>
       <c r="C32" t="s">
         <v>23</v>
@@ -1938,10 +1951,10 @@
         <v>15</v>
       </c>
       <c r="J32" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="K32" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.3">
@@ -1949,7 +1962,7 @@
         <v>44.3</v>
       </c>
       <c r="B33" t="s">
-        <v>113</v>
+        <v>162</v>
       </c>
       <c r="C33" t="s">
         <v>23</v>
@@ -1970,10 +1983,10 @@
         <v>15</v>
       </c>
       <c r="J33" t="s">
-        <v>114</v>
+        <v>95</v>
       </c>
       <c r="K33" t="s">
-        <v>115</v>
+        <v>96</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.3">
@@ -1981,7 +1994,7 @@
         <v>45.7</v>
       </c>
       <c r="B34" t="s">
-        <v>116</v>
+        <v>163</v>
       </c>
       <c r="C34" t="s">
         <v>23</v>
@@ -2005,10 +2018,10 @@
         <v>15</v>
       </c>
       <c r="J34" t="s">
-        <v>117</v>
+        <v>97</v>
       </c>
       <c r="K34" t="s">
-        <v>118</v>
+        <v>98</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.3">
@@ -2016,7 +2029,7 @@
         <v>47.1</v>
       </c>
       <c r="B35" t="s">
-        <v>119</v>
+        <v>164</v>
       </c>
       <c r="C35" t="s">
         <v>23</v>
@@ -2040,10 +2053,10 @@
         <v>15</v>
       </c>
       <c r="J35" t="s">
-        <v>120</v>
+        <v>99</v>
       </c>
       <c r="K35" t="s">
-        <v>121</v>
+        <v>100</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.3">
@@ -2051,13 +2064,13 @@
         <v>48.5</v>
       </c>
       <c r="B36" t="s">
-        <v>122</v>
+        <v>165</v>
       </c>
       <c r="C36" t="s">
         <v>44</v>
       </c>
       <c r="D36" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E36" s="1">
         <v>46101</v>
@@ -2075,10 +2088,10 @@
         <v>15</v>
       </c>
       <c r="J36" t="s">
-        <v>123</v>
+        <v>101</v>
       </c>
       <c r="K36" t="s">
-        <v>124</v>
+        <v>102</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.3">
@@ -2086,13 +2099,13 @@
         <v>49.9</v>
       </c>
       <c r="B37" t="s">
-        <v>125</v>
+        <v>166</v>
       </c>
       <c r="C37" t="s">
         <v>44</v>
       </c>
       <c r="D37" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E37" s="1">
         <v>46069</v>
@@ -2110,10 +2123,10 @@
         <v>15</v>
       </c>
       <c r="J37" t="s">
-        <v>126</v>
+        <v>103</v>
       </c>
       <c r="K37" t="s">
-        <v>127</v>
+        <v>104</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.3">
@@ -2121,13 +2134,13 @@
         <v>51.3</v>
       </c>
       <c r="B38" t="s">
-        <v>128</v>
+        <v>167</v>
       </c>
       <c r="C38" t="s">
         <v>44</v>
       </c>
       <c r="D38" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E38" s="1">
         <v>46055</v>
@@ -2145,10 +2158,10 @@
         <v>15</v>
       </c>
       <c r="J38" t="s">
-        <v>129</v>
+        <v>105</v>
       </c>
       <c r="K38" t="s">
-        <v>130</v>
+        <v>106</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.3">
@@ -2156,13 +2169,13 @@
         <v>52.7</v>
       </c>
       <c r="B39" t="s">
-        <v>131</v>
+        <v>107</v>
       </c>
       <c r="C39" t="s">
         <v>44</v>
       </c>
       <c r="D39" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E39" s="1">
         <v>46086</v>
@@ -2180,10 +2193,10 @@
         <v>15</v>
       </c>
       <c r="J39" t="s">
-        <v>132</v>
+        <v>108</v>
       </c>
       <c r="K39" t="s">
-        <v>133</v>
+        <v>109</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.3">
@@ -2191,13 +2204,13 @@
         <v>54.1</v>
       </c>
       <c r="B40" t="s">
-        <v>134</v>
+        <v>110</v>
       </c>
       <c r="C40" t="s">
         <v>44</v>
       </c>
       <c r="D40" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E40" s="1">
         <v>46083</v>
@@ -2215,10 +2228,10 @@
         <v>15</v>
       </c>
       <c r="J40" t="s">
-        <v>135</v>
+        <v>111</v>
       </c>
       <c r="K40" t="s">
-        <v>136</v>
+        <v>112</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.3">
@@ -2226,13 +2239,13 @@
         <v>55.5</v>
       </c>
       <c r="B41" t="s">
-        <v>137</v>
+        <v>113</v>
       </c>
       <c r="C41" t="s">
         <v>44</v>
       </c>
       <c r="D41" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E41" s="1">
         <v>46082</v>
@@ -2250,10 +2263,10 @@
         <v>15</v>
       </c>
       <c r="J41" t="s">
-        <v>138</v>
+        <v>114</v>
       </c>
       <c r="K41" t="s">
-        <v>139</v>
+        <v>115</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.3">
@@ -2261,13 +2274,13 @@
         <v>56.9</v>
       </c>
       <c r="B42" t="s">
-        <v>140</v>
+        <v>168</v>
       </c>
       <c r="C42" t="s">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="D42" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="E42" s="1">
         <v>46077</v>
@@ -2285,10 +2298,10 @@
         <v>15</v>
       </c>
       <c r="J42" t="s">
-        <v>141</v>
+        <v>116</v>
       </c>
       <c r="K42" t="s">
-        <v>142</v>
+        <v>117</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.3">
@@ -2296,13 +2309,13 @@
         <v>58.3</v>
       </c>
       <c r="B43" t="s">
-        <v>143</v>
+        <v>169</v>
       </c>
       <c r="C43" t="s">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="D43" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="E43" s="1">
         <v>46076</v>
@@ -2320,10 +2333,10 @@
         <v>15</v>
       </c>
       <c r="J43" t="s">
-        <v>144</v>
+        <v>118</v>
       </c>
       <c r="K43" t="s">
-        <v>145</v>
+        <v>119</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.3">
@@ -2331,13 +2344,13 @@
         <v>59.7</v>
       </c>
       <c r="B44" t="s">
-        <v>146</v>
+        <v>170</v>
       </c>
       <c r="C44" t="s">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="D44" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="E44" s="1">
         <v>46071</v>
@@ -2355,10 +2368,10 @@
         <v>36</v>
       </c>
       <c r="J44" t="s">
-        <v>147</v>
+        <v>120</v>
       </c>
       <c r="K44" t="s">
-        <v>148</v>
+        <v>121</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.3">
@@ -2366,13 +2379,13 @@
         <v>61.1</v>
       </c>
       <c r="B45" t="s">
-        <v>149</v>
+        <v>171</v>
       </c>
       <c r="C45" t="s">
-        <v>150</v>
+        <v>122</v>
       </c>
       <c r="D45" t="s">
-        <v>151</v>
+        <v>123</v>
       </c>
       <c r="E45" s="1">
         <v>46093</v>
@@ -2390,10 +2403,10 @@
         <v>36</v>
       </c>
       <c r="J45" t="s">
-        <v>152</v>
+        <v>124</v>
       </c>
       <c r="K45" t="s">
-        <v>153</v>
+        <v>125</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.3">
@@ -2401,7 +2414,7 @@
         <v>62</v>
       </c>
       <c r="B46" t="s">
-        <v>154</v>
+        <v>172</v>
       </c>
       <c r="C46" t="s">
         <v>23</v>
@@ -2425,10 +2438,10 @@
         <v>15</v>
       </c>
       <c r="J46" t="s">
-        <v>155</v>
+        <v>126</v>
       </c>
       <c r="K46" t="s">
-        <v>156</v>
+        <v>127</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.3">
@@ -2436,13 +2449,13 @@
         <v>63</v>
       </c>
       <c r="B47" t="s">
-        <v>169</v>
+        <v>140</v>
       </c>
       <c r="C47" t="s">
         <v>44</v>
       </c>
       <c r="D47" t="s">
-        <v>170</v>
+        <v>141</v>
       </c>
       <c r="E47" s="2">
         <v>46095</v>
@@ -2460,10 +2473,45 @@
         <v>15</v>
       </c>
       <c r="J47" t="s">
-        <v>171</v>
+        <v>142</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>172</v>
+        <v>143</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A48">
+        <v>64</v>
+      </c>
+      <c r="B48" t="s">
+        <v>173</v>
+      </c>
+      <c r="C48" t="s">
+        <v>44</v>
+      </c>
+      <c r="D48" t="s">
+        <v>141</v>
+      </c>
+      <c r="E48" s="2">
+        <v>46101</v>
+      </c>
+      <c r="F48" t="s">
+        <v>20</v>
+      </c>
+      <c r="G48" s="2">
+        <v>46193</v>
+      </c>
+      <c r="H48" t="s">
+        <v>14</v>
+      </c>
+      <c r="I48" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J48" t="s">
+        <v>174</v>
+      </c>
+      <c r="K48" s="2" t="s">
+        <v>175</v>
       </c>
     </row>
   </sheetData>
